--- a/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/7. 特殊开账.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/7. 特殊开账.xlsx
@@ -1097,7 +1097,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1134,13 +1134,6 @@
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1632,46 +1625,49 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1683,97 +1679,94 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2650,7 +2643,7 @@
         <v>98</v>
       </c>
       <c r="R6" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S6" s="4"/>
       <c r="T6" s="5" t="s">
@@ -2740,7 +2733,7 @@
         <v>98</v>
       </c>
       <c r="R7" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S7" s="4"/>
       <c r="T7" s="5" t="s">
@@ -3100,7 +3093,7 @@
         <v>98</v>
       </c>
       <c r="R11" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S11" s="4"/>
       <c r="T11" s="5" t="s">
@@ -3554,7 +3547,7 @@
         <v>98</v>
       </c>
       <c r="R16" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S16" s="4"/>
       <c r="T16" s="5" t="s">
@@ -3644,7 +3637,7 @@
         <v>98</v>
       </c>
       <c r="R17" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S17" s="4"/>
       <c r="T17" s="5" t="s">
@@ -3734,7 +3727,7 @@
         <v>98</v>
       </c>
       <c r="R18" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S18" s="4"/>
       <c r="T18" s="5" t="s">
@@ -3824,7 +3817,7 @@
         <v>98</v>
       </c>
       <c r="R19" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S19" s="4"/>
       <c r="T19" s="5" t="s">
@@ -4094,7 +4087,7 @@
         <v>98</v>
       </c>
       <c r="R22" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S22" s="4"/>
       <c r="T22" s="5" t="s">
@@ -4364,7 +4357,7 @@
         <v>98</v>
       </c>
       <c r="R25" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S25" s="4"/>
       <c r="T25" s="5" t="s">
@@ -4454,7 +4447,7 @@
         <v>98</v>
       </c>
       <c r="R26" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S26" s="4"/>
       <c r="T26" s="5" t="s">
@@ -4544,7 +4537,7 @@
         <v>98</v>
       </c>
       <c r="R27" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S27" s="4"/>
       <c r="T27" s="5" t="s">
@@ -4634,7 +4627,7 @@
         <v>98</v>
       </c>
       <c r="R28" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S28" s="4"/>
       <c r="T28" s="5" t="s">
@@ -4814,7 +4807,7 @@
         <v>98</v>
       </c>
       <c r="R30" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S30" s="4"/>
       <c r="T30" s="5" t="s">
@@ -5084,7 +5077,7 @@
         <v>98</v>
       </c>
       <c r="R33" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S33" s="4"/>
       <c r="T33" s="5" t="s">
@@ -5174,7 +5167,7 @@
         <v>98</v>
       </c>
       <c r="R34" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S34" s="4"/>
       <c r="T34" s="5" t="s">
@@ -5264,7 +5257,7 @@
         <v>98</v>
       </c>
       <c r="R35" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S35" s="4"/>
       <c r="T35" s="5" t="s">
@@ -5354,7 +5347,7 @@
         <v>98</v>
       </c>
       <c r="R36" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S36" s="4"/>
       <c r="T36" s="5" t="s">
@@ -5534,7 +5527,7 @@
         <v>98</v>
       </c>
       <c r="R38" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S38" s="4"/>
       <c r="T38" s="5" t="s">
@@ -5806,7 +5799,7 @@
         <v>98</v>
       </c>
       <c r="R41" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S41" s="4"/>
       <c r="T41" s="5" t="s">
@@ -5896,7 +5889,7 @@
         <v>98</v>
       </c>
       <c r="R42" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S42" s="4"/>
       <c r="T42" s="5" t="s">
@@ -6706,7 +6699,7 @@
         <v>98</v>
       </c>
       <c r="R51" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S51" s="4"/>
       <c r="T51" s="5" t="s">
@@ -6796,7 +6789,7 @@
         <v>98</v>
       </c>
       <c r="R52" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S52" s="4"/>
       <c r="T52" s="5" t="s">
@@ -6886,7 +6879,7 @@
         <v>98</v>
       </c>
       <c r="R53" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S53" s="4"/>
       <c r="T53" s="5" t="s">
@@ -7156,7 +7149,7 @@
         <v>98</v>
       </c>
       <c r="R56" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S56" s="4"/>
       <c r="T56" s="5" t="s">
